--- a/Download/farms_ZP.xlsx
+++ b/Download/farms_ZP.xlsx
@@ -237,7 +237,7 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>

--- a/Download/farms_ZP.xlsx
+++ b/Download/farms_ZP.xlsx
@@ -289,7 +289,7 @@
         <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G7" t="n">
         <v>4.0</v>
@@ -315,10 +315,10 @@
         <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H8" t="n">
         <v>0.0</v>
@@ -341,10 +341,10 @@
         <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0</v>
+        <v>19.0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H9" t="n">
         <v>0.0</v>
@@ -367,10 +367,10 @@
         <v>18</v>
       </c>
       <c r="F10" t="n">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="G10" t="n">
-        <v>11.0</v>
+        <v>60.0</v>
       </c>
       <c r="H10" t="n">
         <v>0.0</v>
@@ -393,10 +393,10 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="G11" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="H11" t="n">
         <v>0.0</v>
@@ -419,10 +419,10 @@
         <v>16</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H12" t="n">
         <v>0.0</v>

--- a/Download/farms_ZP.xlsx
+++ b/Download/farms_ZP.xlsx
@@ -370,7 +370,7 @@
         <v>18.0</v>
       </c>
       <c r="G10" t="n">
-        <v>60.0</v>
+        <v>59.0</v>
       </c>
       <c r="H10" t="n">
         <v>0.0</v>

--- a/Download/farms_ZP.xlsx
+++ b/Download/farms_ZP.xlsx
@@ -240,7 +240,7 @@
         <v>3.0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H5" t="n">
         <v>0.0</v>
@@ -341,7 +341,7 @@
         <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="G9" t="n">
         <v>13.0</v>
@@ -396,7 +396,7 @@
         <v>15.0</v>
       </c>
       <c r="G11" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="H11" t="n">
         <v>0.0</v>

--- a/Download/farms_ZP.xlsx
+++ b/Download/farms_ZP.xlsx
@@ -370,7 +370,7 @@
         <v>18.0</v>
       </c>
       <c r="G10" t="n">
-        <v>59.0</v>
+        <v>58.0</v>
       </c>
       <c r="H10" t="n">
         <v>0.0</v>
